--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484653_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484653_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4252</v>
+        <v>6.018</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0679</v>
+        <v>5.0819</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3573</v>
+        <v>0.9361</v>
       </c>
       <c r="G2" t="n">
         <v>2.59</v>
@@ -610,13 +610,13 @@
         <v>1.8326</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1755</v>
+        <v>1.7683</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7851</v>
+        <v>0.799</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3904</v>
+        <v>0.9692</v>
       </c>
       <c r="V2" t="n">
         <v>0.0104</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8913</v>
+        <v>4.1526</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7992</v>
+        <v>3.0606</v>
       </c>
       <c r="F3" t="n">
         <v>1.0921</v>
@@ -688,10 +688,10 @@
         <v>1.2828</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.1701</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5143</v>
+        <v>-0.253</v>
       </c>
       <c r="U3" t="n">
         <v>0.4231</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3106</v>
+        <v>3.1659</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3213</v>
+        <v>1.8545</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9893</v>
+        <v>1.3114</v>
       </c>
       <c r="G4" t="n">
         <v>3.0243</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5692</v>
+        <v>1.4244</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1878</v>
+        <v>0.721</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3813</v>
+        <v>0.7034</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2748</v>
+        <v>2.0742</v>
       </c>
       <c r="E5" t="n">
-        <v>3.457</v>
+        <v>3.4298</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1822</v>
+        <v>-1.3556</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2144</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2222</v>
+        <v>1.0217</v>
       </c>
       <c r="T5" t="n">
-        <v>0.365</v>
+        <v>0.3379</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8572</v>
+        <v>0.6838</v>
       </c>
       <c r="V5" t="n">
         <v>1.267</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7986</v>
+        <v>1.7823</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6654</v>
+        <v>1.6243</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1332</v>
+        <v>0.158</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7517</v>
@@ -922,13 +922,13 @@
         <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0897</v>
+        <v>0.0733</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2557</v>
+        <v>0.2146</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.166</v>
+        <v>-0.1412</v>
       </c>
       <c r="V6" t="n">
         <v>1.9109</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1853</v>
+        <v>-0.1502</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0264</v>
+        <v>1.7654</v>
       </c>
       <c r="F7" t="n">
-        <v>0.159</v>
+        <v>-1.9155</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2817</v>
+        <v>0.0464</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2589</v>
+        <v>0.1711</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0228</v>
+        <v>-0.1247</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0988</v>
+        <v>1.7167</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7553</v>
+        <v>0.2384</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3434</v>
+        <v>1.4783</v>
       </c>
       <c r="M7" t="n">
-        <v>0.183</v>
+        <v>-1.6703</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5036</v>
+        <v>-0.0673</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3207</v>
+        <v>-1.603</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1991</v>
+        <v>1.0995</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9321</v>
+        <v>-0.1833</v>
       </c>
       <c r="R7" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7362</v>
+        <v>0.2928</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8597</v>
+        <v>0.2319</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1235</v>
+        <v>0.0609</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6335</v>
+        <v>-1.5889</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6335</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CONDE BARBERA</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.867</v>
+        <v>-0.2488</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8396</v>
+        <v>-0.3582</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0275</v>
+        <v>0.1094</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0669</v>
+        <v>2.2817</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4515</v>
+        <v>1.2589</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3846</v>
+        <v>1.0228</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6194</v>
+        <v>2.0988</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6194</v>
+        <v>0.7553</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.3434</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5525</v>
+        <v>0.183</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1679</v>
+        <v>0.5036</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3846</v>
+        <v>-0.3207</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3665</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8447</v>
+        <v>0.302</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2202</v>
+        <v>0.4751</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.1731</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>J. CONDE BARBERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1012</v>
+        <v>-0.6499</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0372</v>
+        <v>-0.6473</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1385</v>
+        <v>-0.0027</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0464</v>
+        <v>-0.0669</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1711</v>
+        <v>-0.4515</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1247</v>
+        <v>0.3846</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7167</v>
+        <v>-0.6194</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2384</v>
+        <v>-0.6194</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4783</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6703</v>
+        <v>0.5525</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0673</v>
+        <v>0.1679</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.603</v>
+        <v>0.3846</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6583</v>
+        <v>-0.6276</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4962</v>
+        <v>-0.0279</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1621</v>
+        <v>-0.5997</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5889</v>
+        <v>-0.3219</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5889</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4689</v>
+        <v>-1.6306</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.859</v>
+        <v>-3.2437</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3901</v>
+        <v>1.6131</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8808</v>
@@ -1234,13 +1234,13 @@
         <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>0.129</v>
+        <v>-0.0326</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7496</v>
+        <v>0.365</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6206</v>
+        <v>-0.3976</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>P. BALAGUER BARBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3787</v>
+        <v>-2.1448</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2354</v>
+        <v>-1.8673</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1433</v>
+        <v>-0.2775</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9074</v>
+        <v>-2.5705</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0544</v>
+        <v>-1.1377</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9618</v>
+        <v>-1.4328</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.243</v>
+        <v>-2.4574</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4361</v>
+        <v>-1.217</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.6791</v>
+        <v>-1.2404</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6644</v>
+        <v>-0.1131</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3818</v>
+        <v>0.0793</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2827</v>
+        <v>-0.1925</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6493</v>
+        <v>0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8326</v>
+        <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4133</v>
+        <v>0.2425</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0761</v>
+        <v>0.5901</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4895</v>
+        <v>-0.3477</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.8009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. BALAGUER BARBA</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7247</v>
+        <v>-2.1975</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3481</v>
+        <v>0.2182</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3766</v>
+        <v>-2.4158</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5705</v>
+        <v>-2.9074</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1377</v>
+        <v>0.0544</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4328</v>
+        <v>-2.9618</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4574</v>
+        <v>-1.243</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.217</v>
+        <v>0.4361</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2404</v>
+        <v>-1.6791</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1131</v>
+        <v>-1.6644</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0793</v>
+        <v>-0.3818</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1925</v>
+        <v>-1.2827</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1833</v>
+        <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3374</v>
+        <v>1.5944</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1094</v>
+        <v>0.3775</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4468</v>
+        <v>1.217</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-3.8009</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.345300000000002</v>
+        <v>10.1712</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0923</v>
+        <v>10.9182</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7471000000000001</v>
+        <v>-0.7470000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>1.572399999999999</v>
@@ -1450,10 +1450,10 @@
         <v>-0.6380999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.918500000000001</v>
+        <v>-4.9185</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4284999999999998</v>
+        <v>-0.4285</v>
       </c>
       <c r="O13" t="n">
         <v>-4.4903</v>
@@ -1468,13 +1468,13 @@
         <v>10.9955</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4034</v>
+        <v>6.229299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0055</v>
+        <v>3.8312</v>
       </c>
       <c r="U13" t="n">
-        <v>2.398</v>
+        <v>2.3981</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2118</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.8125</v>
+        <v>8.533099999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>9.0038</v>
+        <v>7.9461</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8087</v>
+        <v>0.587</v>
       </c>
       <c r="G14" t="n">
         <v>3.8186</v>
@@ -1546,13 +1546,13 @@
         <v>1.2828</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5045</v>
+        <v>0.2251</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3447</v>
+        <v>-0.713</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1598</v>
+        <v>0.9381</v>
       </c>
       <c r="V14" t="n">
         <v>4.1229</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6046</v>
+        <v>2.3724</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9643</v>
+        <v>2.2527</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3597</v>
+        <v>0.1197</v>
       </c>
       <c r="G15" t="n">
         <v>2.5736</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.969</v>
+        <v>-0.2012</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2753</v>
+        <v>0.0132</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6937</v>
+        <v>-0.2144</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9721</v>
+        <v>1.1439</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5243</v>
+        <v>-0.332</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4964</v>
+        <v>1.4759</v>
       </c>
       <c r="G16" t="n">
         <v>1.0704</v>
@@ -1702,13 +1702,13 @@
         <v>0.733</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0849</v>
+        <v>0.2568</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3673</v>
+        <v>-0.175</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4522</v>
+        <v>0.4317</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. CARRION BALLESTER</t>
+          <t>S. HERNANDEZ BENACHES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0771</v>
+        <v>-0.1979</v>
       </c>
       <c r="E17" t="n">
-        <v>0.049</v>
+        <v>2.6962</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1261</v>
+        <v>-2.8941</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7785</v>
+        <v>2.8947</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.5281</v>
+        <v>-0.5547</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2503</v>
+        <v>3.4494</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.2056</v>
+        <v>3.8613</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.3723</v>
+        <v>0.5077</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1667</v>
+        <v>3.3536</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5729</v>
+        <v>-0.9667</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1558</v>
+        <v>-1.0624</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.417</v>
+        <v>0.0958</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1833</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6701</v>
+        <v>-0.632</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9728</v>
+        <v>-0.2489</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3027</v>
+        <v>-0.3831</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5548</v>
+        <v>-1.9109</v>
       </c>
       <c r="W17" t="n">
-        <v>4.1437</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5889</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HERNANDEZ BENACHES</t>
+          <t>R. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.515</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1193</v>
+        <v>0.2413</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.6343</v>
+        <v>-0.8405</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8947</v>
+        <v>-2.7785</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5547</v>
+        <v>-2.5281</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4494</v>
+        <v>-0.2503</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8613</v>
+        <v>-2.2056</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5077</v>
+        <v>-2.3723</v>
       </c>
       <c r="L18" t="n">
-        <v>3.3536</v>
+        <v>0.1667</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9667</v>
+        <v>-0.5729</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0624</v>
+        <v>-0.1558</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0958</v>
+        <v>-0.417</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5498</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3665</v>
+        <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.949</v>
+        <v>-0.1923</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8258</v>
+        <v>-0.7805</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1232</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.9109</v>
+        <v>2.5548</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.1437</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.9109</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7365</v>
+        <v>-1.4874</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5326</v>
+        <v>-1.8211</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2039</v>
+        <v>0.3337</v>
       </c>
       <c r="G19" t="n">
         <v>0.8329</v>
@@ -1936,13 +1936,13 @@
         <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5695</v>
+        <v>-0.3203</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4419</v>
+        <v>-0.7304</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1276</v>
+        <v>0.41</v>
       </c>
       <c r="V19" t="n">
         <v>-1.267</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4415</v>
+        <v>-2.1122</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5333</v>
+        <v>-2.6294</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.5173</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8404</v>
@@ -2014,13 +2014,13 @@
         <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0959</v>
+        <v>0.2334</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1086</v>
+        <v>0.0125</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2045</v>
+        <v>0.221</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3219</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2472</v>
+        <v>-3.0272</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9964</v>
+        <v>-2.2848</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2508</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4785</v>
@@ -2092,13 +2092,13 @@
         <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.431</v>
+        <v>-0.211</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6214</v>
+        <v>0.333</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0524</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0.3115</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4107</v>
+        <v>-3.3932</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3382</v>
+        <v>-0.6266</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0726</v>
+        <v>-2.7666</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8647</v>
@@ -2170,13 +2170,13 @@
         <v>0.1833</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1424</v>
+        <v>0.1599</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7315</v>
+        <v>0.4431</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5891</v>
+        <v>-0.2832</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9554</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.3064</v>
+        <v>-6.7314</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4645</v>
+        <v>-4.6952</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.842</v>
+        <v>-2.0362</v>
       </c>
       <c r="G23" t="n">
         <v>-4.8007</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4507</v>
+        <v>-0.8757</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3212</v>
+        <v>-0.552</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1295</v>
+        <v>-0.3237</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3219</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.345200000000002</v>
+        <v>-5.499200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7470999999999997</v>
+        <v>0.7472000000000012</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.0925</v>
+        <v>-6.2462</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5726</v>
+        <v>-1.572600000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-6.700600000000001</v>
@@ -2299,7 +2299,7 @@
         <v>5.1282</v>
       </c>
       <c r="J24" t="n">
-        <v>4.918399999999999</v>
+        <v>4.9184</v>
       </c>
       <c r="K24" t="n">
         <v>0.4283000000000006</v>
@@ -2326,19 +2326,19 @@
         <v>6.4139</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.4034</v>
+        <v>-1.5573</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.3981</v>
+        <v>-2.398</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.0053</v>
+        <v>0.8407000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>2.2121</v>
       </c>
       <c r="W24" t="n">
-        <v>9.222</v>
+        <v>9.221999999999998</v>
       </c>
       <c r="X24" t="n">
         <v>-7.009900000000001</v>
